--- a/reports/Debug-snowbowl-20260106/For The Day (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260106/For The Day (Actual)_Revenue.xlsx
@@ -55,10 +55,10 @@
     <t>account</t>
   </si>
   <si>
+    <t xml:space="preserve">T103                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T100                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T103                     </t>
   </si>
   <si>
     <t>department</t>
@@ -493,7 +493,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="2">
-        <v>92617.0500</v>
+        <v>7016.6900</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -507,7 +507,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>7016.6900</v>
+        <v>92617.0500</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -591,7 +591,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="2">
-        <v>16358.3900</v>
+        <v>16379.8900</v>
       </c>
     </row>
     <row r="11" spans="1:4">
